--- a/english.xlsx
+++ b/english.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="72">
   <si>
     <t>id</t>
   </si>
@@ -94,9 +94,6 @@
   </si>
   <si>
     <t>(あなたが)楽しみにされているでしょう</t>
-  </si>
-  <si>
-    <t>Good for you.</t>
   </si>
   <si>
     <t>よかったですね</t>
@@ -131,7 +128,117 @@
   </si>
   <si>
     <r>
-      <t>エモリさんが、1ヶ月ほど私のところに滞在</t>
+      <t xml:space="preserve">It's been </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>quite a while</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> since we last saw each other.</t>
+    </r>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <r>
+      <t>最後に会ってから</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ずいぶん(かなり長い間)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>経ちます</t>
+    </r>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <r>
+      <t>He</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> will be </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>stay</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with me for about a month.</t>
+    </r>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <r>
+      <t>彼が1ヶ月ほど私のところに滞在</t>
     </r>
     <r>
       <rPr>
@@ -145,11 +252,165 @@
       </rPr>
       <t>することになります</t>
     </r>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <r>
-      <t>He</t>
+    <rPh sb="0" eb="1">
+      <t>カレ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>祝意</t>
+    <rPh sb="0" eb="2">
+      <t>シュクイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Good on you.だと温かみが増す。</t>
+    <rPh sb="14" eb="15">
+      <t>アタタ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>マ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>I'm happy for you.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>それは素晴らしい！</t>
+    <rPh sb="3" eb="5">
+      <t>スバ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Nice.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>I got the job.--よかったね(淡白)</t>
+    <rPh sb="22" eb="24">
+      <t>タンパク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Sweet.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>I got the job.--よかったねぇ(共感)</t>
+    <rPh sb="23" eb="25">
+      <t>キョウカン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>あなたはそれに値します</t>
+    <rPh sb="7" eb="8">
+      <t>アタイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>You deserve it.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>評価</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウカ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>It paid off.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>報われましたね</t>
+    <rPh sb="0" eb="1">
+      <t>ムク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>I knew you could do it.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>あなたならできると思っていました</t>
+    <rPh sb="9" eb="10">
+      <t>オモ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>That's great to hear.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>聞いてよかったよ</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>それを聞いてよかったよ</t>
+    <rPh sb="3" eb="4">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>I'm glad[pleased] to hear that.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>That's great[wonderful/awesome]!</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <r>
+      <t>Goo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0" tint="-0.14999847407452621"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for you.</t>
+    </r>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>新婚旅行の行き先はもう決めてあるの？</t>
+    <rPh sb="0" eb="4">
+      <t>シンコンリョコウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Do you have a haneymoon spot </t>
     </r>
     <r>
       <rPr>
@@ -161,7 +422,7 @@
         <charset val="128"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> will be </t>
+      <t>picked out</t>
     </r>
     <r>
       <rPr>
@@ -172,7 +433,49 @@
         <charset val="128"/>
         <scheme val="minor"/>
       </rPr>
-      <t>stay</t>
+      <t>?</t>
+    </r>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>a haneymoon spot=picked outの状態をhaveしている=決めてある</t>
+    <rPh sb="28" eb="30">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>The plush turned out great, and we've added the voice feature as discussed.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ぬいぐるみの仕上がりもとてもよく、打ち合わせ通り、音声機能も追加しております</t>
+    <rPh sb="6" eb="8">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ドオ</t>
+    </rPh>
+    <rPh sb="25" eb="29">
+      <t>オンセイキノウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I'd like you to review the current flow and identify wher users might get confused or </t>
     </r>
     <r>
       <rPr>
@@ -184,7 +487,7 @@
         <charset val="128"/>
         <scheme val="minor"/>
       </rPr>
-      <t>ing</t>
+      <t>drop off</t>
     </r>
     <r>
       <rPr>
@@ -195,13 +498,24 @@
         <charset val="128"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> with me for about a month.</t>
-    </r>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">It's been </t>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>正確さ</t>
+    <rPh sb="0" eb="2">
+      <t>セイカク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Should I also look into improving the search accuracy?</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Let's </t>
     </r>
     <r>
       <rPr>
@@ -213,28 +527,10 @@
         <charset val="128"/>
         <scheme val="minor"/>
       </rPr>
-      <t>quite a while</t>
+      <t>aim for</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> since we last saw each other.</t>
-    </r>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <r>
-      <t>最後に会ってから</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="ＭＳ Ｐゴシック"/>
@@ -242,19 +538,60 @@
         <charset val="128"/>
         <scheme val="minor"/>
       </rPr>
-      <t>ずいぶん(かなり長い間)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>経ちます</t>
-    </r>
+      <t xml:space="preserve"> a smoother, moreuser-friendly experience overall.</t>
+    </r>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>I see.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Got it.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Understood.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>了解</t>
+    <rPh sb="0" eb="2">
+      <t>リョウカイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>わかりました</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>I'll get right on it.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>あなたには現在の導線を見直して、ユーザーがどこで混乱したり、途中で離脱したりするのか特定してほしいんです</t>
+    <rPh sb="5" eb="7">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ドウセン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ミナオ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>コンラン</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>トチュウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>リダツ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>トクテイ</t>
+    </rPh>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -262,7 +599,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -424,6 +761,22 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.14999847407452621"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -857,9 +1210,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1182,10 +1538,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="30.81640625" customWidth="1"/>
+    <col min="4" max="4" width="37.6328125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="43.08984375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -1198,27 +1555,27 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="26" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
@@ -1232,10 +1589,10 @@
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1246,10 +1603,10 @@
       <c r="C4">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F4" t="s">
@@ -1266,10 +1623,10 @@
       <c r="C5">
         <v>1</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1283,10 +1640,10 @@
       <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1300,10 +1657,10 @@
       <c r="C7">
         <v>1</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1317,10 +1674,10 @@
       <c r="C8">
         <v>1</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1334,14 +1691,14 @@
       <c r="C9">
         <v>1</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="26" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>6</v>
       </c>
@@ -1351,11 +1708,11 @@
       <c r="C10">
         <v>81</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E10" t="s">
-        <v>32</v>
+      <c r="E10" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -1365,57 +1722,330 @@
       <c r="C11">
         <v>81</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="26" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>8</v>
       </c>
       <c r="C12">
         <v>81</v>
       </c>
-      <c r="D12" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="D12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="26" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>9</v>
+      </c>
+      <c r="C13">
+        <v>81</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>10</v>
+      </c>
+      <c r="C14">
+        <v>81</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>11</v>
+      </c>
+      <c r="B15" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="D13" t="s">
+      <c r="C15">
+        <v>81</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="D14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="D15" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" t="s">
-        <v>30</v>
+      <c r="F15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16">
+        <v>81</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17">
+        <v>81</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18">
+        <v>81</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19">
+        <v>81</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20">
+        <v>81</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21">
+        <v>81</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>16</v>
+      </c>
+      <c r="B22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22">
+        <v>81</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>17</v>
+      </c>
+      <c r="B23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23">
+        <v>81</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>18</v>
+      </c>
+      <c r="B24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24">
+        <v>81</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="26" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>19</v>
+      </c>
+      <c r="C25">
+        <v>81</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F25" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="26" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>20</v>
+      </c>
+      <c r="C26">
+        <v>82</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="39" x14ac:dyDescent="0.2">
+      <c r="C27">
+        <v>96</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="26" x14ac:dyDescent="0.2">
+      <c r="D28" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="26" x14ac:dyDescent="0.2">
+      <c r="D29" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B31" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B32" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D33" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18"/>
+  <hyperlinks>
+    <hyperlink ref="A24" r:id="rId1" display="\\"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
 </worksheet>
 </file>
--- a/english.xlsx
+++ b/english.xlsx
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="88">
   <si>
     <t>id</t>
   </si>
@@ -370,10 +370,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>That's great[wonderful/awesome]!</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <r>
       <t>Goo</t>
     </r>
@@ -503,13 +499,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>正確さ</t>
-    <rPh sb="0" eb="2">
-      <t>セイカク</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>Should I also look into improving the search accuracy?</t>
     <phoneticPr fontId="18"/>
   </si>
@@ -566,11 +555,45 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>I'll get right on it.</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>あなたには現在の導線を見直して、ユーザーがどこで混乱したり、途中で離脱したりするのか特定してほしいんです</t>
+    <t>検索精度の改善についても検討したほうがいいですか？</t>
+    <rPh sb="0" eb="4">
+      <t>ケンサクセイド</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ケントウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <r>
+      <t>あなたには現在の導線を見直して、ユーザーがどこで混乱したり、途中で</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>離脱した</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>りするのか特定してほしいんです</t>
+    </r>
     <rPh sb="5" eb="7">
       <t>ゲンザイ</t>
     </rPh>
@@ -592,6 +615,257 @@
     <rPh sb="42" eb="44">
       <t>トクテイ</t>
     </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <r>
+      <t>全体として、もっとスムーズでユーザーが使いやすい体験を</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>目指し</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ましょう</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>ゼンタイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <r>
+      <t>すぐに</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>とりかかり</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ます</t>
+    </r>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>すぐに始めます</t>
+    <rPh sb="3" eb="4">
+      <t>ハジ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>I'll get started[begin] right away.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>直ちに対応いたします(formal)</t>
+    <rPh sb="0" eb="1">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>I'll take care of it right away.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>I'll get to work on it.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>(I'm) on it.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>やります。やってます(casual)</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>I'll drive[jump] right in.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>すぐにやります（やる気）</t>
+    <rPh sb="10" eb="11">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>I'll get cracking.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>すぐにやります</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>crack=殻などを割る</t>
+    <rPh sb="6" eb="7">
+      <t>カラ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Do you want me to fold everything as well? Or we could team up and get It done quickly.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>全部畳むのも私にやってほしい？それとも一緒にやって、さっさと終わらせることもできるね</t>
+    <rPh sb="0" eb="3">
+      <t>ゼンブタタ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>イッショ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I'll </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ge</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0" tint="-0.14999847407452621"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> righ</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">t </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>on</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0" tint="-0.14999847407452621"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>That's great[wonderful/awesome]!</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -599,7 +873,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -777,6 +1051,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0" tint="-0.14999847407452621"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -1538,7 +1840,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="37.6328125" style="1" customWidth="1"/>
@@ -1785,7 +2087,7 @@
         <v>81</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>25</v>
@@ -1856,7 +2158,7 @@
         <v>81</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>38</v>
@@ -1955,13 +2257,13 @@
         <v>81</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F25" t="s">
         <v>57</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F25" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="26" x14ac:dyDescent="0.2">
@@ -1972,72 +2274,229 @@
         <v>82</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="27" spans="1:6" ht="39" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <f>A26+1</f>
+        <v>21</v>
+      </c>
       <c r="C27">
         <v>96</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="26" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <f t="shared" ref="A28:A30" si="0">A27+1</f>
+        <v>22</v>
+      </c>
+      <c r="C28">
+        <v>96</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E28" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="26" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="C29">
+        <v>96</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30">
+        <v>96</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <f>A30</f>
+        <v>24</v>
+      </c>
+      <c r="B31" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31">
+        <v>96</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <f>A31+1</f>
+        <v>25</v>
+      </c>
+      <c r="B32" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32">
+        <v>96</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <f>A32</f>
+        <v>25</v>
+      </c>
+      <c r="C33">
+        <v>96</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="26" x14ac:dyDescent="0.2">
-      <c r="D28" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="26" x14ac:dyDescent="0.2">
-      <c r="D29" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B30" t="s">
-        <v>68</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B31" t="s">
-        <v>68</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B32" t="s">
-        <v>68</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D33" s="1" t="s">
-        <v>70</v>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <f>A33</f>
+        <v>25</v>
+      </c>
+      <c r="C34">
+        <v>96</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <f>A34</f>
+        <v>25</v>
+      </c>
+      <c r="C35">
+        <v>96</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <f>A35+1</f>
+        <v>26</v>
+      </c>
+      <c r="C36">
+        <v>96</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <f>A36+1</f>
+        <v>27</v>
+      </c>
+      <c r="C37">
+        <v>96</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <f>A37+1</f>
+        <v>28</v>
+      </c>
+      <c r="C38">
+        <v>96</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <f>A38</f>
+        <v>28</v>
+      </c>
+      <c r="C39">
+        <v>96</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F39" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="39" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <f>A39+1</f>
+        <v>29</v>
+      </c>
+      <c r="C40">
+        <v>96</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/english.xlsx
+++ b/english.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="138">
   <si>
     <t>id</t>
   </si>
@@ -866,6 +866,594 @@
   </si>
   <si>
     <t>That's great[wonderful/awesome]!</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Mom is asking us to mow the lawn this afternoon.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>お母さんが今日の午後、私たちに芝刈りをしてほしいって言ってるよ</t>
+    <rPh sb="1" eb="2">
+      <t>カア</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ゴゴ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>シバカ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>それなら</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>…よし</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>やるよ(参加する)</t>
+    </r>
+    <rPh sb="11" eb="13">
+      <t>サンカ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>In that case</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>…yeah,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> I'm in.</t>
+    </r>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <r>
+      <t>やることが山ほどあるし、宿題にも</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>どっぷりつかってる</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>んだよ</t>
+    </r>
+    <rPh sb="5" eb="6">
+      <t>ヤマ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シュクダイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>I'm a bit busy[occupied/tied up] right now.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>今ちょっと忙しいのです</t>
+    <rPh sb="0" eb="1">
+      <t>イマ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>イソガ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Things have been hectic.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>非常に慌ただしいのです</t>
+    <rPh sb="0" eb="2">
+      <t>ヒジョウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>アワ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>I'm a bit overwhelmed right now.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>今はちょっと、いっぱいいっぱいなんだ</t>
+    <rPh sb="0" eb="1">
+      <t>イマ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>I'm stretched thin at work.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>仕事で手が回りません</t>
+    <rPh sb="0" eb="2">
+      <t>シゴト</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>テ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>マワ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>My schedule is packed today.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>私のスケジュールは今日いっぱいです</t>
+    <rPh sb="0" eb="1">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キョウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>waist-deep, neck-deepと深くなっていく</t>
+    <rPh sb="22" eb="23">
+      <t>フカ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>There's no end in sight.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>終わりが見えない</t>
+    <rPh sb="0" eb="1">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <r>
+      <t>I've go</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>t a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> lo</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>t o</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>n my pla</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0" tint="-0.14999847407452621"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>te,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and I'm</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> knee-deep</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in homework.</t>
+    </r>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Hi, I'd like to make a reservation for tonight.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Around 7:30, if possible.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>We have a table available. How many people will be in your party?</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>It'll be for two.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>May I have your name, please?</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>We'll see you at 7:30</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>See you then.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>こんにちは、今夜の予約をお願いしたいのですが</t>
+    <rPh sb="6" eb="8">
+      <t>コンヤ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヨヤク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ネガ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>お時間は何時頃をご希望ですか？</t>
+    <rPh sb="1" eb="3">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ナンジゴロ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キボウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>可能であれば、7時半ころでお願いします</t>
+    <rPh sb="0" eb="2">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジハン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ネガ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>お席をご用意できます。ご利用は何名様でしょうか？</t>
+    <rPh sb="1" eb="2">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヨウイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>ナンメイサマ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>二人です</t>
+    <rPh sb="0" eb="2">
+      <t>フタリ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>お名前を頂戴してもよろしいでしょうか？</t>
+    <rPh sb="1" eb="3">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>チョウダイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>7時半にお待ちしております</t>
+    <rPh sb="1" eb="3">
+      <t>ジハン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>マ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>それではまたそのときに</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">What time </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>were</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> you thinking?</t>
+    </r>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>areだと直接的だから過去形にして距離を取って丁寧にしている</t>
+    <rPh sb="5" eb="8">
+      <t>チョクセツテキ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>カコケイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>テイネイ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>I'd like to make a reservation for two at 7:30 tonight.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>今夜7時半に二人で予約したいのです</t>
+    <rPh sb="0" eb="2">
+      <t>コンヤ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジハン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>フタリ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヨヤク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>予約</t>
+    <rPh sb="0" eb="2">
+      <t>ヨヤク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Let me confirm the spelling.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>スペルを確認させてください</t>
+    <rPh sb="4" eb="6">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>I'd like a table where it's quiet, if possible.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>デキれば静かな席をお願いします</t>
+    <rPh sb="4" eb="5">
+      <t>シズ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ネガ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>We might be a bit late.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>少し遅れるかもしれません</t>
+    <rPh sb="0" eb="1">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>We'll be about ten minutes late.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>10分ほど遅れます</t>
+    <rPh sb="2" eb="3">
+      <t>プン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>オク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>無断キャンセル</t>
+    <rPh sb="0" eb="2">
+      <t>ムダン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>no-show</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Table for two.</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -1512,11 +2100,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1840,7 +2431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="37.6328125" style="1" customWidth="1"/>
@@ -2499,6 +3090,383 @@
         <v>85</v>
       </c>
     </row>
+    <row r="41" spans="1:6" ht="26" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <f>A40+1</f>
+        <v>30</v>
+      </c>
+      <c r="C41">
+        <v>97</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <f t="shared" ref="A42:A44" si="1">A41+1</f>
+        <v>31</v>
+      </c>
+      <c r="C42">
+        <v>97</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="26" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="C43">
+        <v>97</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F43" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="C44">
+        <v>97</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <f>A44</f>
+        <v>33</v>
+      </c>
+      <c r="C45">
+        <v>97</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <f>A45</f>
+        <v>33</v>
+      </c>
+      <c r="C46">
+        <v>97</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <f>A46</f>
+        <v>33</v>
+      </c>
+      <c r="C47">
+        <v>97</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <f>A47</f>
+        <v>33</v>
+      </c>
+      <c r="C48">
+        <v>97</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <f>A48</f>
+        <v>33</v>
+      </c>
+      <c r="C49">
+        <v>97</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <f>A49+1</f>
+        <v>34</v>
+      </c>
+      <c r="B50" t="s">
+        <v>126</v>
+      </c>
+      <c r="C50">
+        <v>98</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="26" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <f>A50</f>
+        <v>34</v>
+      </c>
+      <c r="B51" t="s">
+        <v>126</v>
+      </c>
+      <c r="C51">
+        <v>98</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <f>A51+1</f>
+        <v>35</v>
+      </c>
+      <c r="C52">
+        <v>98</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F52" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <f t="shared" ref="A53:A55" si="2">A52+1</f>
+        <v>36</v>
+      </c>
+      <c r="C53">
+        <v>98</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="26" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <f t="shared" si="2"/>
+        <v>37</v>
+      </c>
+      <c r="C54">
+        <v>98</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <f t="shared" si="2"/>
+        <v>38</v>
+      </c>
+      <c r="C55">
+        <v>98</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <f>A55</f>
+        <v>38</v>
+      </c>
+      <c r="C56">
+        <v>98</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <f>A55+1</f>
+        <v>39</v>
+      </c>
+      <c r="C57">
+        <v>98</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <f>A57+1</f>
+        <v>40</v>
+      </c>
+      <c r="C58">
+        <v>98</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <f t="shared" ref="A59:A64" si="3">A58+1</f>
+        <v>41</v>
+      </c>
+      <c r="C59">
+        <v>98</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="C60">
+        <v>98</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="C61">
+        <v>98</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="C62">
+        <v>98</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="C63">
+        <v>98</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="C64">
+        <v>98</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="65" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C65">
+        <v>99</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18"/>
   <hyperlinks>

--- a/english.xlsx
+++ b/english.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="152">
   <si>
     <t>id</t>
   </si>
@@ -1280,13 +1280,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>二人です</t>
-    <rPh sb="0" eb="2">
-      <t>フタリ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>お名前を頂戴してもよろしいでしょうか？</t>
     <rPh sb="1" eb="3">
       <t>ナマエ</t>
@@ -1454,6 +1447,231 @@
   </si>
   <si>
     <t>Table for two.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Hi, this is David Evans. I have a reservation for tonight at 7:30.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>How can I help you?</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Just give us a call when you're ready.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>もしもし、デイビット・エヴァンスです。今夜7時半に予約をしています</t>
+    <rPh sb="19" eb="21">
+      <t>コンヤ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ジハン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ヨヤク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>いかがなさいましたか？</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ご都合がよろしい時にお電話ください</t>
+    <rPh sb="1" eb="3">
+      <t>ツゴウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>デンワ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I'm really sorry, but </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>something came up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, and I </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>won't be able to</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>make it.</t>
+    </r>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <r>
+      <t>大変申し訳ないのですが、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>用事ができて(問題が起きて)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>しまって、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>行け(成功・参加）</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>そうにありません</t>
+    </r>
+    <rPh sb="0" eb="3">
+      <t>タイヘンモウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ワケ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヨウジ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>サンカ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>すぐにとりかかります</t>
+  </si>
+  <si>
+    <t>start</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>busy</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>(予約は)二人です</t>
+    <rPh sb="1" eb="3">
+      <t>ヨヤク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>フタリ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>cancel</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>I'm calling to cancel my reservation for tonight.</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>今夜の予約をキャンセルしたくてお電話しました</t>
+    <rPh sb="0" eb="2">
+      <t>コンヤ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヨヤク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>デンワ</t>
+    </rPh>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -1461,7 +1679,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1667,6 +1885,15 @@
     <font>
       <b/>
       <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2431,7 +2658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="37.6328125" style="1" customWidth="1"/>
@@ -2975,6 +3202,9 @@
         <f>A32</f>
         <v>25</v>
       </c>
+      <c r="B33" t="s">
+        <v>146</v>
+      </c>
       <c r="C33">
         <v>96</v>
       </c>
@@ -2990,11 +3220,17 @@
         <f>A33</f>
         <v>25</v>
       </c>
+      <c r="B34" t="s">
+        <v>146</v>
+      </c>
       <c r="C34">
         <v>96</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>76</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
@@ -3002,6 +3238,9 @@
         <f>A34</f>
         <v>25</v>
       </c>
+      <c r="B35" t="s">
+        <v>146</v>
+      </c>
       <c r="C35">
         <v>96</v>
       </c>
@@ -3017,6 +3256,9 @@
         <f>A35+1</f>
         <v>26</v>
       </c>
+      <c r="B36" t="s">
+        <v>146</v>
+      </c>
       <c r="C36">
         <v>96</v>
       </c>
@@ -3032,6 +3274,9 @@
         <f>A36+1</f>
         <v>27</v>
       </c>
+      <c r="B37" t="s">
+        <v>146</v>
+      </c>
       <c r="C37">
         <v>96</v>
       </c>
@@ -3047,6 +3292,9 @@
         <f>A37+1</f>
         <v>28</v>
       </c>
+      <c r="B38" t="s">
+        <v>146</v>
+      </c>
       <c r="C38">
         <v>96</v>
       </c>
@@ -3059,8 +3307,11 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39">
-        <f>A38</f>
-        <v>28</v>
+        <f>A38+1</f>
+        <v>29</v>
+      </c>
+      <c r="B39" t="s">
+        <v>146</v>
       </c>
       <c r="C39">
         <v>96</v>
@@ -3078,7 +3329,7 @@
     <row r="40" spans="1:6" ht="39" x14ac:dyDescent="0.2">
       <c r="A40">
         <f>A39+1</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C40">
         <v>96</v>
@@ -3093,7 +3344,7 @@
     <row r="41" spans="1:6" ht="26" x14ac:dyDescent="0.2">
       <c r="A41">
         <f>A40+1</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C41">
         <v>97</v>
@@ -3108,7 +3359,7 @@
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42">
         <f t="shared" ref="A42:A44" si="1">A41+1</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C42">
         <v>97</v>
@@ -3123,7 +3374,10 @@
     <row r="43" spans="1:6" ht="26" x14ac:dyDescent="0.2">
       <c r="A43">
         <f t="shared" si="1"/>
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="B43" t="s">
+        <v>147</v>
       </c>
       <c r="C43">
         <v>97</v>
@@ -3141,7 +3395,10 @@
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44">
         <f t="shared" si="1"/>
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="B44" t="s">
+        <v>147</v>
       </c>
       <c r="C44">
         <v>97</v>
@@ -3156,7 +3413,10 @@
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45">
         <f>A44</f>
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="B45" t="s">
+        <v>147</v>
       </c>
       <c r="C45">
         <v>97</v>
@@ -3171,7 +3431,10 @@
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46">
         <f>A45</f>
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="B46" t="s">
+        <v>147</v>
       </c>
       <c r="C46">
         <v>97</v>
@@ -3186,7 +3449,10 @@
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47">
         <f>A46</f>
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="B47" t="s">
+        <v>147</v>
       </c>
       <c r="C47">
         <v>97</v>
@@ -3201,7 +3467,10 @@
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48">
         <f>A47</f>
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="B48" t="s">
+        <v>147</v>
       </c>
       <c r="C48">
         <v>97</v>
@@ -3216,7 +3485,10 @@
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49">
         <f>A48</f>
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="B49" t="s">
+        <v>147</v>
       </c>
       <c r="C49">
         <v>97</v>
@@ -3231,10 +3503,10 @@
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50">
         <f>A49+1</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B50" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C50">
         <v>98</v>
@@ -3249,43 +3521,43 @@
     <row r="51" spans="1:6" ht="26" x14ac:dyDescent="0.2">
       <c r="A51">
         <f>A50</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B51" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C51">
         <v>98</v>
       </c>
       <c r="D51" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52">
         <f>A51+1</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C52">
         <v>98</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>115</v>
       </c>
       <c r="F52" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53">
         <f t="shared" ref="A53:A55" si="2">A52+1</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C53">
         <v>98</v>
@@ -3300,7 +3572,7 @@
     <row r="54" spans="1:6" ht="26" x14ac:dyDescent="0.2">
       <c r="A54">
         <f t="shared" si="2"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C54">
         <v>98</v>
@@ -3315,7 +3587,7 @@
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55">
         <f t="shared" si="2"/>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C55">
         <v>98</v>
@@ -3324,28 +3596,28 @@
         <v>110</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56">
         <f>A55</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C56">
         <v>98</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57">
         <f>A55+1</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C57">
         <v>98</v>
@@ -3354,28 +3626,28 @@
         <v>111</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58">
         <f>A57+1</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C58">
         <v>98</v>
       </c>
       <c r="D58" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59">
         <f t="shared" ref="A59:A64" si="3">A58+1</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C59">
         <v>98</v>
@@ -3384,13 +3656,13 @@
         <v>112</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C60">
         <v>98</v>
@@ -3399,72 +3671,116 @@
         <v>113</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61">
         <f t="shared" si="3"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C61">
         <v>98</v>
       </c>
       <c r="D61" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62">
         <f t="shared" si="3"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C62">
         <v>98</v>
       </c>
       <c r="D62" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63">
         <f t="shared" si="3"/>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C63">
         <v>98</v>
       </c>
       <c r="D63" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64">
         <f t="shared" si="3"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C64">
         <v>98</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="65" spans="3:3" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5" ht="26" x14ac:dyDescent="0.2">
       <c r="C65">
         <v>99</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="66" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="D66" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5" ht="39" x14ac:dyDescent="0.2">
+      <c r="B67" t="s">
+        <v>149</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="68" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="D68" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="69" spans="2:5" ht="26" x14ac:dyDescent="0.2">
+      <c r="B69" t="s">
+        <v>149</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
